--- a/Data/testDataPoland4.xlsx
+++ b/Data/testDataPoland4.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="27328"/>
   <workbookPr filterPrivacy="1"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:20001_{663AD489-4E40-4E61-856A-87190201CCD4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1F6A8D23-F355-4590-BB9E-D4703D8C0E61}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -11,7 +11,6 @@
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
   <calcPr calcId="191029"/>
-  <fileRecoveryPr repairLoad="1"/>
   <extLst>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
       <xcalcf:calcFeatures>
@@ -1961,7 +1960,7 @@
       </c>
       <c r="K2" s="15">
         <f t="shared" ref="K2:K7" ca="1" si="0">TODAY()-31</f>
-        <v>45573</v>
+        <v>45677</v>
       </c>
       <c r="L2" s="10" t="s">
         <v>61</v>
@@ -2001,7 +2000,7 @@
       </c>
       <c r="X2" s="19">
         <f t="shared" ref="X2:X7" ca="1" si="1">K2</f>
-        <v>45573</v>
+        <v>45677</v>
       </c>
       <c r="Y2" s="14" t="s">
         <v>74</v>
@@ -2047,11 +2046,11 @@
       </c>
       <c r="AM2" s="25">
         <f t="shared" ref="AM2:AM7" ca="1" si="2">X2</f>
-        <v>45573</v>
+        <v>45677</v>
       </c>
       <c r="AN2" s="25">
         <f t="shared" ref="AN2:AN7" ca="1" si="3">X2</f>
-        <v>45573</v>
+        <v>45677</v>
       </c>
       <c r="AO2" s="26" t="str">
         <f t="shared" ref="AO2:AO16" si="4">AI2</f>
@@ -2148,7 +2147,7 @@
       </c>
       <c r="K3" s="15">
         <f t="shared" ca="1" si="0"/>
-        <v>45573</v>
+        <v>45677</v>
       </c>
       <c r="L3" s="10" t="s">
         <v>61</v>
@@ -2188,7 +2187,7 @@
       </c>
       <c r="X3" s="19">
         <f t="shared" ca="1" si="1"/>
-        <v>45573</v>
+        <v>45677</v>
       </c>
       <c r="Y3" s="14" t="s">
         <v>74</v>
@@ -2234,11 +2233,11 @@
       </c>
       <c r="AM3" s="25">
         <f t="shared" ca="1" si="2"/>
-        <v>45573</v>
+        <v>45677</v>
       </c>
       <c r="AN3" s="25">
         <f t="shared" ca="1" si="3"/>
-        <v>45573</v>
+        <v>45677</v>
       </c>
       <c r="AO3" s="26" t="str">
         <f t="shared" si="4"/>
@@ -2335,7 +2334,7 @@
       </c>
       <c r="K4" s="15">
         <f t="shared" ca="1" si="0"/>
-        <v>45573</v>
+        <v>45677</v>
       </c>
       <c r="L4" s="10" t="s">
         <v>61</v>
@@ -2375,7 +2374,7 @@
       </c>
       <c r="X4" s="19">
         <f t="shared" ca="1" si="1"/>
-        <v>45573</v>
+        <v>45677</v>
       </c>
       <c r="Y4" s="14" t="s">
         <v>74</v>
@@ -2421,11 +2420,11 @@
       </c>
       <c r="AM4" s="25">
         <f t="shared" ca="1" si="2"/>
-        <v>45573</v>
+        <v>45677</v>
       </c>
       <c r="AN4" s="25">
         <f t="shared" ca="1" si="3"/>
-        <v>45573</v>
+        <v>45677</v>
       </c>
       <c r="AO4" s="26" t="str">
         <f t="shared" si="4"/>
@@ -2522,7 +2521,7 @@
       </c>
       <c r="K5" s="15">
         <f t="shared" ca="1" si="0"/>
-        <v>45573</v>
+        <v>45677</v>
       </c>
       <c r="L5" s="10" t="s">
         <v>61</v>
@@ -2562,7 +2561,7 @@
       </c>
       <c r="X5" s="19">
         <f t="shared" ca="1" si="1"/>
-        <v>45573</v>
+        <v>45677</v>
       </c>
       <c r="Y5" s="14" t="s">
         <v>74</v>
@@ -2596,7 +2595,7 @@
       </c>
       <c r="AI5" s="24">
         <f ca="1">TODAY()+365</f>
-        <v>45969</v>
+        <v>46073</v>
       </c>
       <c r="AJ5" s="14" t="s">
         <v>82</v>
@@ -2609,15 +2608,15 @@
       </c>
       <c r="AM5" s="25">
         <f t="shared" ca="1" si="2"/>
-        <v>45573</v>
+        <v>45677</v>
       </c>
       <c r="AN5" s="25">
         <f t="shared" ca="1" si="3"/>
-        <v>45573</v>
+        <v>45677</v>
       </c>
       <c r="AO5" s="26">
         <f t="shared" ca="1" si="4"/>
-        <v>45969</v>
+        <v>46073</v>
       </c>
       <c r="AP5" s="23" t="s">
         <v>85</v>
@@ -2710,7 +2709,7 @@
       </c>
       <c r="K6" s="15">
         <f t="shared" ca="1" si="0"/>
-        <v>45573</v>
+        <v>45677</v>
       </c>
       <c r="L6" s="10" t="s">
         <v>61</v>
@@ -2750,7 +2749,7 @@
       </c>
       <c r="X6" s="19">
         <f t="shared" ca="1" si="1"/>
-        <v>45573</v>
+        <v>45677</v>
       </c>
       <c r="Y6" s="14" t="s">
         <v>74</v>
@@ -2796,11 +2795,11 @@
       </c>
       <c r="AM6" s="25">
         <f t="shared" ca="1" si="2"/>
-        <v>45573</v>
+        <v>45677</v>
       </c>
       <c r="AN6" s="25">
         <f t="shared" ca="1" si="3"/>
-        <v>45573</v>
+        <v>45677</v>
       </c>
       <c r="AO6" s="43" t="str">
         <f t="shared" si="4"/>
@@ -2897,7 +2896,7 @@
       </c>
       <c r="K7" s="15">
         <f t="shared" ca="1" si="0"/>
-        <v>45573</v>
+        <v>45677</v>
       </c>
       <c r="L7" s="10" t="s">
         <v>61</v>
@@ -2937,7 +2936,7 @@
       </c>
       <c r="X7" s="19">
         <f t="shared" ca="1" si="1"/>
-        <v>45573</v>
+        <v>45677</v>
       </c>
       <c r="Y7" s="14" t="s">
         <v>74</v>
@@ -2983,11 +2982,11 @@
       </c>
       <c r="AM7" s="25">
         <f t="shared" ca="1" si="2"/>
-        <v>45573</v>
+        <v>45677</v>
       </c>
       <c r="AN7" s="25">
         <f t="shared" ca="1" si="3"/>
-        <v>45573</v>
+        <v>45677</v>
       </c>
       <c r="AO7" s="43" t="str">
         <f t="shared" si="4"/>
@@ -3084,7 +3083,7 @@
       </c>
       <c r="K8" s="15">
         <f t="shared" ref="K8:K10" ca="1" si="5">TODAY()-31</f>
-        <v>45573</v>
+        <v>45677</v>
       </c>
       <c r="L8" s="10" t="s">
         <v>61</v>
@@ -3124,7 +3123,7 @@
       </c>
       <c r="X8" s="19">
         <f t="shared" ref="X8:X10" ca="1" si="6">K8</f>
-        <v>45573</v>
+        <v>45677</v>
       </c>
       <c r="Y8" s="14" t="s">
         <v>74</v>
@@ -3158,7 +3157,7 @@
       </c>
       <c r="AI8" s="41">
         <f ca="1">TODAY()+365</f>
-        <v>45969</v>
+        <v>46073</v>
       </c>
       <c r="AJ8" s="14" t="s">
         <v>82</v>
@@ -3171,15 +3170,15 @@
       </c>
       <c r="AM8" s="25">
         <f t="shared" ref="AM8:AM10" ca="1" si="7">X8</f>
-        <v>45573</v>
+        <v>45677</v>
       </c>
       <c r="AN8" s="25">
         <f t="shared" ref="AN8:AN10" ca="1" si="8">X8</f>
-        <v>45573</v>
+        <v>45677</v>
       </c>
       <c r="AO8" s="43">
         <f t="shared" ca="1" si="4"/>
-        <v>45969</v>
+        <v>46073</v>
       </c>
       <c r="AP8" s="23" t="s">
         <v>85</v>
@@ -3272,7 +3271,7 @@
       </c>
       <c r="K9" s="15">
         <f t="shared" ca="1" si="5"/>
-        <v>45573</v>
+        <v>45677</v>
       </c>
       <c r="L9" s="10" t="s">
         <v>61</v>
@@ -3312,7 +3311,7 @@
       </c>
       <c r="X9" s="19">
         <f t="shared" ca="1" si="6"/>
-        <v>45573</v>
+        <v>45677</v>
       </c>
       <c r="Y9" s="14" t="s">
         <v>74</v>
@@ -3346,7 +3345,7 @@
       </c>
       <c r="AI9" s="41">
         <f ca="1">TODAY()+365</f>
-        <v>45969</v>
+        <v>46073</v>
       </c>
       <c r="AJ9" s="14" t="s">
         <v>82</v>
@@ -3359,15 +3358,15 @@
       </c>
       <c r="AM9" s="25">
         <f t="shared" ca="1" si="7"/>
-        <v>45573</v>
+        <v>45677</v>
       </c>
       <c r="AN9" s="25">
         <f t="shared" ca="1" si="8"/>
-        <v>45573</v>
+        <v>45677</v>
       </c>
       <c r="AO9" s="43">
         <f t="shared" ca="1" si="4"/>
-        <v>45969</v>
+        <v>46073</v>
       </c>
       <c r="AP9" s="23" t="s">
         <v>85</v>
@@ -3460,7 +3459,7 @@
       </c>
       <c r="K10" s="15">
         <f t="shared" ca="1" si="5"/>
-        <v>45573</v>
+        <v>45677</v>
       </c>
       <c r="L10" s="10" t="s">
         <v>61</v>
@@ -3500,7 +3499,7 @@
       </c>
       <c r="X10" s="19">
         <f t="shared" ca="1" si="6"/>
-        <v>45573</v>
+        <v>45677</v>
       </c>
       <c r="Y10" s="14" t="s">
         <v>74</v>
@@ -3546,11 +3545,11 @@
       </c>
       <c r="AM10" s="25">
         <f t="shared" ca="1" si="7"/>
-        <v>45573</v>
+        <v>45677</v>
       </c>
       <c r="AN10" s="25">
         <f t="shared" ca="1" si="8"/>
-        <v>45573</v>
+        <v>45677</v>
       </c>
       <c r="AO10" s="43" t="str">
         <f t="shared" si="4"/>
@@ -3647,7 +3646,7 @@
       </c>
       <c r="K11" s="15">
         <f t="shared" ref="K11:K16" ca="1" si="9">TODAY()-31</f>
-        <v>45573</v>
+        <v>45677</v>
       </c>
       <c r="L11" s="10" t="s">
         <v>61</v>
@@ -3687,7 +3686,7 @@
       </c>
       <c r="X11" s="19">
         <f t="shared" ref="X11" ca="1" si="10">K11</f>
-        <v>45573</v>
+        <v>45677</v>
       </c>
       <c r="Y11" s="14" t="s">
         <v>74</v>
@@ -3733,11 +3732,11 @@
       </c>
       <c r="AM11" s="25">
         <f ca="1">X11</f>
-        <v>45573</v>
+        <v>45677</v>
       </c>
       <c r="AN11" s="25">
         <f ca="1">X11</f>
-        <v>45573</v>
+        <v>45677</v>
       </c>
       <c r="AO11" s="43" t="str">
         <f t="shared" si="4"/>
@@ -3834,7 +3833,7 @@
       </c>
       <c r="K12" s="15">
         <f t="shared" ca="1" si="9"/>
-        <v>45573</v>
+        <v>45677</v>
       </c>
       <c r="L12" s="10" t="s">
         <v>61</v>
@@ -3874,7 +3873,7 @@
       </c>
       <c r="X12" s="19">
         <f t="shared" ref="X12" ca="1" si="11">K12</f>
-        <v>45573</v>
+        <v>45677</v>
       </c>
       <c r="Y12" s="14" t="s">
         <v>74</v>
@@ -3920,11 +3919,11 @@
       </c>
       <c r="AM12" s="25">
         <f ca="1">X12</f>
-        <v>45573</v>
+        <v>45677</v>
       </c>
       <c r="AN12" s="25">
         <f ca="1">X12</f>
-        <v>45573</v>
+        <v>45677</v>
       </c>
       <c r="AO12" s="43" t="str">
         <f t="shared" si="4"/>
@@ -4021,7 +4020,7 @@
       </c>
       <c r="K13" s="15">
         <f t="shared" ca="1" si="9"/>
-        <v>45573</v>
+        <v>45677</v>
       </c>
       <c r="L13" s="10" t="s">
         <v>61</v>
@@ -4061,7 +4060,7 @@
       </c>
       <c r="X13" s="19">
         <f t="shared" ref="X13" ca="1" si="12">K13</f>
-        <v>45573</v>
+        <v>45677</v>
       </c>
       <c r="Y13" s="14" t="s">
         <v>74</v>
@@ -4095,7 +4094,7 @@
       </c>
       <c r="AI13" s="41">
         <f ca="1">TODAY()+365</f>
-        <v>45969</v>
+        <v>46073</v>
       </c>
       <c r="AJ13" s="14" t="s">
         <v>82</v>
@@ -4108,15 +4107,15 @@
       </c>
       <c r="AM13" s="25">
         <f ca="1">X13</f>
-        <v>45573</v>
+        <v>45677</v>
       </c>
       <c r="AN13" s="25">
         <f ca="1">X13</f>
-        <v>45573</v>
+        <v>45677</v>
       </c>
       <c r="AO13" s="43">
         <f t="shared" ca="1" si="4"/>
-        <v>45969</v>
+        <v>46073</v>
       </c>
       <c r="AP13" s="23" t="s">
         <v>162</v>
@@ -4209,7 +4208,7 @@
       </c>
       <c r="K14" s="15">
         <f t="shared" ca="1" si="9"/>
-        <v>45573</v>
+        <v>45677</v>
       </c>
       <c r="L14" s="10" t="s">
         <v>61</v>
@@ -4249,7 +4248,7 @@
       </c>
       <c r="X14" s="19">
         <f t="shared" ref="X14:X16" ca="1" si="13">K14</f>
-        <v>45573</v>
+        <v>45677</v>
       </c>
       <c r="Y14" s="14" t="s">
         <v>74</v>
@@ -4295,11 +4294,11 @@
       </c>
       <c r="AM14" s="25">
         <f t="shared" ref="AM14:AM16" ca="1" si="14">X14</f>
-        <v>45573</v>
+        <v>45677</v>
       </c>
       <c r="AN14" s="25">
         <f t="shared" ref="AN14:AN16" ca="1" si="15">X14</f>
-        <v>45573</v>
+        <v>45677</v>
       </c>
       <c r="AO14" s="43" t="str">
         <f t="shared" si="4"/>
@@ -4396,7 +4395,7 @@
       </c>
       <c r="K15" s="15">
         <f t="shared" ca="1" si="9"/>
-        <v>45573</v>
+        <v>45677</v>
       </c>
       <c r="L15" s="10" t="s">
         <v>61</v>
@@ -4436,7 +4435,7 @@
       </c>
       <c r="X15" s="19">
         <f t="shared" ca="1" si="13"/>
-        <v>45573</v>
+        <v>45677</v>
       </c>
       <c r="Y15" s="14" t="s">
         <v>74</v>
@@ -4482,11 +4481,11 @@
       </c>
       <c r="AM15" s="25">
         <f t="shared" ca="1" si="14"/>
-        <v>45573</v>
+        <v>45677</v>
       </c>
       <c r="AN15" s="25">
         <f t="shared" ca="1" si="15"/>
-        <v>45573</v>
+        <v>45677</v>
       </c>
       <c r="AO15" s="43" t="str">
         <f t="shared" si="4"/>
@@ -4583,7 +4582,7 @@
       </c>
       <c r="K16" s="15">
         <f t="shared" ca="1" si="9"/>
-        <v>45573</v>
+        <v>45677</v>
       </c>
       <c r="L16" s="10" t="s">
         <v>61</v>
@@ -4623,7 +4622,7 @@
       </c>
       <c r="X16" s="19">
         <f t="shared" ca="1" si="13"/>
-        <v>45573</v>
+        <v>45677</v>
       </c>
       <c r="Y16" s="14" t="s">
         <v>74</v>
@@ -4657,7 +4656,7 @@
       </c>
       <c r="AI16" s="41">
         <f ca="1">TODAY()+365</f>
-        <v>45969</v>
+        <v>46073</v>
       </c>
       <c r="AJ16" s="14" t="s">
         <v>82</v>
@@ -4670,15 +4669,15 @@
       </c>
       <c r="AM16" s="25">
         <f t="shared" ca="1" si="14"/>
-        <v>45573</v>
+        <v>45677</v>
       </c>
       <c r="AN16" s="25">
         <f t="shared" ca="1" si="15"/>
-        <v>45573</v>
+        <v>45677</v>
       </c>
       <c r="AO16" s="43">
         <f t="shared" ca="1" si="4"/>
-        <v>45969</v>
+        <v>46073</v>
       </c>
       <c r="AP16" s="23" t="s">
         <v>162</v>
